--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED08.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED08.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>201W</t>
+          <t>126W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0026</t>
+          <t>SIM_XA_FIXED-2-0128</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35W</t>
+          <t>122W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第3年</t>
+          <t>第2年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>0季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
     </row>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,14 +2134,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Auction_Win</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
         </is>
       </c>
     </row>
@@ -2167,11 +2167,11 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年2季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2193,11 +2193,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2212,14 +2212,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-15</v>
+        <v>-48</v>
       </c>
       <c r="E19" t="n">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-ca09d32215"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2238,14 +2238,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="E20" t="n">
-        <v>417</v>
+        <v>348</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca09d32215", "asset_type": "factory"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-e160fa7796", "line_id": "L-ca09d32215", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2264,14 +2264,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E21" t="n">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca09d32215", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2290,23 +2290,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="E22" t="n">
-        <v>413</v>
+        <v>319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>maintenance_expense | {"line_id": "L-ca09d32215"}</t>
         </is>
       </c>
     </row>
@@ -2316,23 +2316,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>399</v>
+        <v>319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca09d32215", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2342,23 +2342,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>385</v>
+        <v>319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca09d32215", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2368,23 +2368,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-12</v>
       </c>
       <c r="E25" t="n">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2394,23 +2394,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-37678dc145", "line_id": "L-ca09d32215", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2420,23 +2420,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-14</v>
+        <v>122</v>
       </c>
       <c r="E27" t="n">
-        <v>351</v>
+        <v>415</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0128", "receivable_term_quarters": 0, "revenue_wan": 122.0}</t>
         </is>
       </c>
     </row>
@@ -2446,23 +2446,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E28" t="n">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="E29" t="n">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-ca09d32215"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-8ee189e7d8", "line_id": "L-ca09d32215", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2498,23 +2498,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca09d32215", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2524,23 +2524,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca09d32215", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2550,23 +2550,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0026", "receivable_term_quarters": 4, "revenue_wan": 35.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2576,23 +2576,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E33" t="n">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>maintenance_expense | {"line_id": "L-ca09d32215"}</t>
         </is>
       </c>
     </row>
@@ -2602,23 +2602,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-931503b62f", "line_id": "L-ca09d32215", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca09d32215", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2628,23 +2628,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca09d32215", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2654,14 +2654,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E36" t="n">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2687,11 +2687,11 @@
         <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2713,11 +2713,11 @@
         <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2739,11 +2739,11 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2758,14 +2758,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>35</v>
+        <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-8132c87bd0"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
         <v>-15</v>
       </c>
       <c r="E41" t="n">
-        <v>262</v>
+        <v>195</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>262</v>
+        <v>195</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>262</v>
+        <v>195</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E44" t="n">
-        <v>258</v>
+        <v>183</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3139,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3364,16 +3364,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3429,10 +3429,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3454,10 +3454,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3479,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3501,16 +3501,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3526,16 +3526,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-75</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-75</v>
+        <v>-41</v>
       </c>
       <c r="G20" t="n">
-        <v>-60</v>
+        <v>-83</v>
       </c>
       <c r="H20" t="n">
-        <v>-61</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3576,16 +3576,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-90.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-90.2</v>
+        <v>-56.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-75.2</v>
+        <v>-98.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3626,16 +3626,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-90.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-90.2</v>
+        <v>-56.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-75.2</v>
+        <v>-98.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3676,16 +3676,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-90.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-90.2</v>
+        <v>-56.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-75.2</v>
+        <v>-98.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -3775,16 +3775,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>417</v>
+        <v>319</v>
       </c>
       <c r="F30" t="n">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="G30" t="n">
-        <v>262</v>
+        <v>195</v>
       </c>
       <c r="H30" t="n">
-        <v>201</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3853,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -3900,16 +3900,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="F35" t="n">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="G35" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="H35" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36">
@@ -4025,16 +4025,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>498.6</v>
+        <v>480.6</v>
       </c>
       <c r="F40" t="n">
-        <v>408.4</v>
+        <v>424.4</v>
       </c>
       <c r="G40" t="n">
-        <v>333.2</v>
+        <v>326.2</v>
       </c>
       <c r="H40" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41">
@@ -4203,13 +4203,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-176.4</v>
+        <v>-194.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-266.6</v>
+        <v>-250.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-341.8</v>
+        <v>-348.8</v>
       </c>
     </row>
     <row r="48">
@@ -4225,16 +4225,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-90.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-90.2</v>
+        <v>-56.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-75.2</v>
+        <v>-98.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4250,16 +4250,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>498.6</v>
+        <v>480.6</v>
       </c>
       <c r="F49" t="n">
-        <v>408.4</v>
+        <v>424.4</v>
       </c>
       <c r="G49" t="n">
-        <v>333.2</v>
+        <v>326.2</v>
       </c>
       <c r="H49" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
@@ -4275,16 +4275,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>498.6</v>
+        <v>480.6</v>
       </c>
       <c r="F50" t="n">
-        <v>408.4</v>
+        <v>424.4</v>
       </c>
       <c r="G50" t="n">
-        <v>333.2</v>
+        <v>326.2</v>
       </c>
       <c r="H50" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
